--- a/artfynd/A 62126-2020 artfynd.xlsx
+++ b/artfynd/A 62126-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107941098</v>
       </c>
       <c r="B2" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62126-2020 artfynd.xlsx
+++ b/artfynd/A 62126-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107941098</v>
       </c>
       <c r="B2" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 62126-2020 artfynd.xlsx
+++ b/artfynd/A 62126-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>107941098</v>
       </c>
       <c r="B2" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
